--- a/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>PLTK</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2567000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2615500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2583000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2371500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1887600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1490700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1150800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>931900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>725300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>718500</v>
+      </c>
+      <c r="E9" s="3">
         <v>735700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>729000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>712200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>566300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>437000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>348200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>282400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>227800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1848500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1879800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1854000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1659300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1321300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1053700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>802600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>649500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>497500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>406400</v>
+      </c>
+      <c r="E12" s="3">
         <v>472300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>386700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>268900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>210500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>148300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>107700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>78000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>67000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,14 +904,17 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>51300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -906,24 +925,27 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -954,9 +976,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2065400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2144100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2020800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1984300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1390200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1058100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>817700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>770100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>478700</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>501600</v>
+      </c>
+      <c r="E18" s="3">
         <v>471400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>562200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>387200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>497400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>432600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>333100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>161800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>246600</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,97 +1080,104 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E20" s="3">
         <v>6900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>703100</v>
+      </c>
+      <c r="E21" s="3">
         <v>640300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>703100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>511900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>570900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>468900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>364500</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E22" s="3">
         <v>117500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>149200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>198300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>61600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1146,75 +1185,84 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>392100</v>
+      </c>
+      <c r="E23" s="3">
         <v>360800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>408400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>194400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>436300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>430700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>337800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>158700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>247900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E24" s="3">
         <v>85500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>99900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>102300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>147400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>92700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>80400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>77300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>51900</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E26" s="3">
         <v>275300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>308500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>92100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>288900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>338000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>257400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>196000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E27" s="3">
         <v>275300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>308500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>92100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>288900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>338000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>257400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>81400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>196000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E33" s="3">
         <v>275300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>308500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>92100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>288900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>338000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>257400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>196000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E35" s="3">
         <v>275300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>308500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>92100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>288900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>338000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>257400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>196000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,53 +1729,57 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1029700</v>
+      </c>
+      <c r="E41" s="3">
         <v>768700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1017000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>520100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>266800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>326000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>96900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>153400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>100100</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1706,33 +1795,36 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E43" s="3">
         <v>141100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>143700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>129300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>125700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>161900</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1742,9 +1834,12 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1775,96 +1870,105 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E45" s="3">
         <v>115100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>74900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>105100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>84600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>80400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1000</v>
       </c>
       <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1351100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1024900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1335700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>754500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>477100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>542800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>558500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>191700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>224100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E47" s="3">
         <v>52600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17800</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>10500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1874,63 +1978,69 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E48" s="3">
         <v>229900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>192700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>171900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>140800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1298400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1165200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1205400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>812500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>830900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>371000</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1940,9 +2050,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,30 +2122,33 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>250900</v>
+      </c>
+      <c r="E52" s="3">
         <v>225000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>51700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>37300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>39700</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,9 +2158,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3175000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2697600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2803300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1776200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1480300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1014800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>850200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>373700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>398400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,29 +2265,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E57" s="3">
         <v>50700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>45700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>34600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>54100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,30 +2298,33 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E58" s="3">
         <v>12400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>104600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>137600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>151800</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2201,30 +2334,33 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>457800</v>
+      </c>
+      <c r="E59" s="3">
         <v>398700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>511800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>501200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>362200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>253600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,63 +2370,69 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>539600</v>
+      </c>
+      <c r="E60" s="3">
         <v>461800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>569700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>640400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>553900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>435100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>177600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>99200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>67700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2399600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2411200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2422900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2209800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2319800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10500</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2300,30 +2442,33 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>457300</v>
+      </c>
+      <c r="E62" s="3">
         <v>393200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>188400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>169500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>222100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>104500</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,9 +2478,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,30 +2586,33 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3396500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3266200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3181000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3019700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3095800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>550100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,9 +2622,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-907600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1142600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1417900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1726400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1818500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>258500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>320500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>63100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>196000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-221500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-568600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-377700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1243500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1615500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>464700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>526400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>269000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>321500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E81" s="3">
         <v>275300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>308500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>92100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>288900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>338000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>257400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>196000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E83" s="3">
         <v>162000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>145500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>119200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>73000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26700</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>515600</v>
+      </c>
+      <c r="E89" s="3">
         <v>493700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>551700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>517700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>491900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>452800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>369000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-54100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-41100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15700</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-240200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-74600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-609400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-98100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-516500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-141900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-225900</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-652000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>559700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-181300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-337400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>92000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-15700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>261300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-248600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>495400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>251600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>236700</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>PLTK</t>
   </si>
@@ -842,10 +842,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>406400</v>
+        <v>404600</v>
       </c>
       <c r="E12" s="3">
-        <v>472300</v>
+        <v>459100</v>
       </c>
       <c r="F12" s="3">
         <v>386700</v>
@@ -914,25 +914,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>51300</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+        <v>61000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F14" s="3">
+        <v>36700</v>
+      </c>
+      <c r="G14" s="3">
+        <v>55000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>22400</v>
       </c>
       <c r="I14" s="3">
-        <v>800</v>
+        <v>5800</v>
       </c>
       <c r="J14" s="3">
-        <v>12300</v>
+        <v>13900</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -950,25 +950,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>126300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>137000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>123700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>110300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>72700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>37700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>26700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -999,25 +999,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2065400</v>
+        <v>2004400</v>
       </c>
       <c r="E17" s="3">
-        <v>2144100</v>
+        <v>2116400</v>
       </c>
       <c r="F17" s="3">
-        <v>2020800</v>
+        <v>1984100</v>
       </c>
       <c r="G17" s="3">
-        <v>1984300</v>
+        <v>1929300</v>
       </c>
       <c r="H17" s="3">
-        <v>1390200</v>
+        <v>1367800</v>
       </c>
       <c r="I17" s="3">
-        <v>1058100</v>
+        <v>1052300</v>
       </c>
       <c r="J17" s="3">
-        <v>817700</v>
+        <v>803800</v>
       </c>
       <c r="K17" s="3">
         <v>770100</v>
@@ -1035,25 +1035,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>501600</v>
+        <v>562600</v>
       </c>
       <c r="E18" s="3">
-        <v>471400</v>
+        <v>499100</v>
       </c>
       <c r="F18" s="3">
-        <v>562200</v>
+        <v>598900</v>
       </c>
       <c r="G18" s="3">
-        <v>387200</v>
+        <v>442200</v>
       </c>
       <c r="H18" s="3">
-        <v>497400</v>
+        <v>519800</v>
       </c>
       <c r="I18" s="3">
-        <v>432600</v>
+        <v>438400</v>
       </c>
       <c r="J18" s="3">
-        <v>333100</v>
+        <v>347000</v>
       </c>
       <c r="K18" s="3">
         <v>161800</v>
@@ -1087,25 +1087,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>43500</v>
+        <v>-800</v>
       </c>
       <c r="E20" s="3">
-        <v>6900</v>
+        <v>7200</v>
       </c>
       <c r="F20" s="3">
-        <v>-4600</v>
+        <v>5400</v>
       </c>
       <c r="G20" s="3">
-        <v>5500</v>
+        <v>-5400</v>
       </c>
       <c r="H20" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I20" s="3">
-        <v>-1400</v>
+        <v>6600</v>
       </c>
       <c r="J20" s="3">
-        <v>4700</v>
+        <v>-3200</v>
       </c>
       <c r="K20" s="3">
         <v>-3100</v>
@@ -1123,25 +1123,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>703100</v>
+        <v>689700</v>
       </c>
       <c r="E21" s="3">
-        <v>640300</v>
+        <v>628900</v>
       </c>
       <c r="F21" s="3">
-        <v>703100</v>
+        <v>717200</v>
       </c>
       <c r="G21" s="3">
-        <v>511900</v>
+        <v>557900</v>
       </c>
       <c r="H21" s="3">
-        <v>570900</v>
+        <v>591500</v>
       </c>
       <c r="I21" s="3">
-        <v>468900</v>
+        <v>469500</v>
       </c>
       <c r="J21" s="3">
-        <v>364500</v>
+        <v>376900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1176,8 +1176,8 @@
       <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1519,25 +1519,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-43500</v>
+        <v>800</v>
       </c>
       <c r="E32" s="3">
-        <v>-6900</v>
+        <v>-7200</v>
       </c>
       <c r="F32" s="3">
-        <v>4600</v>
+        <v>-5400</v>
       </c>
       <c r="G32" s="3">
-        <v>-5500</v>
+        <v>5400</v>
       </c>
       <c r="H32" s="3">
-        <v>-500</v>
+        <v>-1000</v>
       </c>
       <c r="I32" s="3">
-        <v>1400</v>
+        <v>-6600</v>
       </c>
       <c r="J32" s="3">
-        <v>-4700</v>
+        <v>3200</v>
       </c>
       <c r="K32" s="3">
         <v>3100</v>
@@ -1753,8 +1753,8 @@
       <c r="I41" s="3">
         <v>300500</v>
       </c>
-      <c r="J41" s="3">
-        <v>326000</v>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>96900</v>
@@ -1771,26 +1771,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>25300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="F42" s="3">
         <v>100100</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1843,26 +1843,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1880,25 +1880,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>149900</v>
+        <v>107200</v>
       </c>
       <c r="E45" s="3">
-        <v>115100</v>
+        <v>77900</v>
       </c>
       <c r="F45" s="3">
-        <v>74900</v>
+        <v>61600</v>
       </c>
       <c r="G45" s="3">
-        <v>105100</v>
+        <v>89600</v>
       </c>
       <c r="H45" s="3">
-        <v>84600</v>
+        <v>72000</v>
       </c>
       <c r="I45" s="3">
-        <v>80400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>8600</v>
+        <v>67700</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>1000</v>
@@ -1933,8 +1933,8 @@
       <c r="I46" s="3">
         <v>542800</v>
       </c>
-      <c r="J46" s="3">
-        <v>558500</v>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>191700</v>
@@ -1952,22 +1952,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>54400</v>
+        <v>69600</v>
       </c>
       <c r="E47" s="3">
-        <v>52600</v>
+        <v>81900</v>
       </c>
       <c r="F47" s="3">
-        <v>17800</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>10500</v>
+        <v>25700</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -2005,8 +2005,8 @@
       <c r="I48" s="3">
         <v>50800</v>
       </c>
-      <c r="J48" s="3">
-        <v>26800</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>20300</v>
@@ -2041,8 +2041,8 @@
       <c r="I49" s="3">
         <v>371000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2132,22 +2132,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>250900</v>
+        <v>136400</v>
       </c>
       <c r="E52" s="3">
-        <v>225000</v>
+        <v>127400</v>
       </c>
       <c r="F52" s="3">
-        <v>51700</v>
+        <v>5500</v>
       </c>
       <c r="G52" s="3">
-        <v>37300</v>
+        <v>7300</v>
       </c>
       <c r="H52" s="3">
-        <v>31500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>39700</v>
+        <v>3300</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2221,8 +2221,8 @@
       <c r="I54" s="3">
         <v>1014800</v>
       </c>
-      <c r="J54" s="3">
-        <v>850200</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>373700</v>
@@ -2308,25 +2308,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16800</v>
+        <v>36300</v>
       </c>
       <c r="E58" s="3">
-        <v>12400</v>
+        <v>25900</v>
       </c>
       <c r="F58" s="3">
-        <v>12200</v>
+        <v>29400</v>
       </c>
       <c r="G58" s="3">
-        <v>104600</v>
+        <v>121000</v>
       </c>
       <c r="H58" s="3">
-        <v>137600</v>
+        <v>148100</v>
       </c>
       <c r="I58" s="3">
         <v>151800</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2344,22 +2344,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>457800</v>
+        <v>127400</v>
       </c>
       <c r="E59" s="3">
-        <v>398700</v>
+        <v>63500</v>
       </c>
       <c r="F59" s="3">
-        <v>511800</v>
+        <v>194100</v>
       </c>
       <c r="G59" s="3">
-        <v>501200</v>
+        <v>189400</v>
       </c>
       <c r="H59" s="3">
-        <v>362200</v>
+        <v>132300</v>
       </c>
       <c r="I59" s="3">
-        <v>253600</v>
+        <v>84000</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2397,8 +2397,8 @@
       <c r="I60" s="3">
         <v>435100</v>
       </c>
-      <c r="J60" s="3">
-        <v>177600</v>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>99200</v>
@@ -2416,19 +2416,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2399600</v>
+        <v>2492200</v>
       </c>
       <c r="E61" s="3">
-        <v>2411200</v>
+        <v>2505700</v>
       </c>
       <c r="F61" s="3">
-        <v>2422900</v>
+        <v>2505200</v>
       </c>
       <c r="G61" s="3">
-        <v>2209800</v>
+        <v>2276800</v>
       </c>
       <c r="H61" s="3">
-        <v>2319800</v>
+        <v>2372200</v>
       </c>
       <c r="I61" s="3">
         <v>10500</v>
@@ -2452,22 +2452,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>457300</v>
+        <v>335100</v>
       </c>
       <c r="E62" s="3">
-        <v>393200</v>
+        <v>252100</v>
       </c>
       <c r="F62" s="3">
-        <v>188400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>169500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>222100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>104500</v>
+        <v>31100</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2809,8 +2809,8 @@
       <c r="I72" s="3">
         <v>258500</v>
       </c>
-      <c r="J72" s="3">
-        <v>320500</v>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>63100</v>
@@ -2953,8 +2953,8 @@
       <c r="I76" s="3">
         <v>464700</v>
       </c>
-      <c r="J76" s="3">
-        <v>526400</v>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>269000</v>
@@ -3101,25 +3101,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>158000</v>
+        <v>45700</v>
       </c>
       <c r="E83" s="3">
-        <v>162000</v>
+        <v>45900</v>
       </c>
       <c r="F83" s="3">
-        <v>145500</v>
+        <v>42500</v>
       </c>
       <c r="G83" s="3">
-        <v>119200</v>
+        <v>37600</v>
       </c>
       <c r="H83" s="3">
-        <v>73000</v>
+        <v>23600</v>
       </c>
       <c r="I83" s="3">
-        <v>37700</v>
+        <v>17500</v>
       </c>
       <c r="J83" s="3">
-        <v>26700</v>
+        <v>9600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3541,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>2365900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>PLTK</t>
   </si>
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2549300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2567000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2615500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2583000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2371500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1887600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1490700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1150800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>931900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>725300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>692100</v>
+      </c>
+      <c r="E9" s="3">
         <v>718500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>735700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>729000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>712200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>566300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>437000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>348200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>282400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>227800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1857200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1848500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1879800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1854000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1659300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1321300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1053700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>802600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>649500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>497500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,44 +848,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>388500</v>
+      </c>
+      <c r="E12" s="3">
         <v>404600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>459100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>386700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>268900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>210500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>148300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>107700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>78000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>67000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,81 +923,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>93300</v>
+      </c>
+      <c r="E14" s="3">
         <v>61000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>27700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>36700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>55000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E15" s="3">
         <v>126300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>137000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>123700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>110300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>72700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>37700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2064400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2004400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2116400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1984100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1929300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1367800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1052300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>803800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>770100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>478700</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>484900</v>
+      </c>
+      <c r="E18" s="3">
         <v>562600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>499100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>598900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>442200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>519800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>438400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>347000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>161800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>246600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,104 +1113,111 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>607900</v>
+      </c>
+      <c r="E21" s="3">
         <v>689700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>628900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>717200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>557900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>591500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>469500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>376900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>153000</v>
+        <v>155200</v>
       </c>
       <c r="E22" s="3">
+        <v>154200</v>
+      </c>
+      <c r="F22" s="3">
         <v>117500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>149200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>198300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>61600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,81 +1227,90 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>280500</v>
+      </c>
+      <c r="E23" s="3">
         <v>392100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>360800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>408400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>194400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>436300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>430700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>337800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>158700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>247900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E24" s="3">
         <v>157100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>85500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>99900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>102300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>147400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>92700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>80400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>77300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>51900</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E26" s="3">
         <v>235000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>275300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>308500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>92100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>288900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>338000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>257400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>196000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E27" s="3">
         <v>235000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>275300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>308500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>92100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>288900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>338000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>257400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>81400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>196000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E33" s="3">
         <v>235000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>275300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>308500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>92100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>288900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>338000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>257400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>81400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>196000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E35" s="3">
         <v>235000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>275300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>308500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>92100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>288900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>338000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>257400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>81400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>196000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,59 +1815,63 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>565800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1029700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>768700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1017000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>520100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>266800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>300500</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>96900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>153400</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E42" s="3">
         <v>25300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>100100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1792,42 +1881,45 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>187600</v>
+      </c>
+      <c r="E43" s="3">
         <v>171500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>141100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>143700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>129300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>125700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>161900</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,9 +1929,12 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1864,8 +1959,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1873,99 +1968,108 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>69900</v>
+      </c>
+      <c r="E45" s="3">
         <v>107200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>77900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>61600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>89600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>72000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>67700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1000</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>872800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1351100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1024900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1335700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>754500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>477100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>542800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>191700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>224100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E47" s="3">
         <v>69600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>81900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1500</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,71 +2085,77 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E48" s="3">
         <v>220200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>229900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>192700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>171900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>140800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>20300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2254500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1298400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1165200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1205400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>812500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>830900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>371000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2053,9 +2163,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,30 +2241,33 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>157200</v>
+      </c>
+      <c r="E52" s="3">
         <v>136400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>127400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3300</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,9 +2280,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,45 +2319,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3639200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3175000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2697600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2803300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1776200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1480300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1014800</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>373700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>398400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,32 +2395,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E57" s="3">
         <v>65000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2301,35 +2431,38 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E58" s="3">
         <v>36300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>25900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>29400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>121000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>148100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>151800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2337,33 +2470,36 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>148100</v>
+      </c>
+      <c r="E59" s="3">
         <v>127400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>63500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>194100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>189400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>132300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>84000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,69 +2509,75 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>558900</v>
+      </c>
+      <c r="E60" s="3">
         <v>539600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>461800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>569700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>640400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>553900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>435100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>99200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>67700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2459900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2492200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2505700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2505200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2276800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2372200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2445,24 +2587,27 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>726800</v>
+      </c>
+      <c r="E62" s="3">
         <v>335100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>252100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,33 +2743,36 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3770300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3396500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3266200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3181000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3019700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3095800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>550100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2625,9 +2782,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,45 +2955,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-894200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-907600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1142600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1417900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1726400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1818500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>258500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>63100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>196000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,45 +3111,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-131100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-221500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-568600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-377700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1243500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1615500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>464700</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>269000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>321500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E81" s="3">
         <v>235000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>275300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>308500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>92100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>288900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>338000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>257400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>81400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>196000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,44 +3292,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E83" s="3">
         <v>45700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>42500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,45 +3523,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>490100</v>
+      </c>
+      <c r="E89" s="3">
         <v>515600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>493700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>551700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>517700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>491900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>452800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>369000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,44 +3582,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-32600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-68300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-47400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-54100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15700</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,45 +3696,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-782100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-240200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-74600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-609400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-98100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-516500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-141900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-225900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,13 +3755,14 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>111500</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3541,14 +3774,14 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>2365900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>400000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,115 +3908,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-167100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-652000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>559700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-181300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-337400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>92000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E101" s="3">
         <v>4100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>13300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-464000</v>
+      </c>
+      <c r="E102" s="3">
         <v>261300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-248600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>495400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>251600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>236700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PLTK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
   <si>
     <t>PLTK</t>
   </si>
@@ -656,184 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2755400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2549300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2567000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2615500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2583000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2371500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1887600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1490700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1150800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>931900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>725300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>758500</v>
+      </c>
+      <c r="E9" s="3">
         <v>692100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>718500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>735700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>729000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>712200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>566300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>437000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>348200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>282400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>227800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1996900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1857200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1848500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1879800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1854000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1659300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1321300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1053700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>802600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>649500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>497500</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,47 +861,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>416900</v>
+      </c>
+      <c r="E12" s="3">
         <v>388500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>404600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>459100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>386700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>268900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>210500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>148300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>107700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>78000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>67000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,87 +942,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E14" s="3">
         <v>93300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>61000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>36700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>55000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>201500</v>
+      </c>
+      <c r="E15" s="3">
         <v>135000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>126300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>137000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>123700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>110300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>72700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>37700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,86 +1044,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2320500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2064400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2004400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2116400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1984100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1929300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1367800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1052300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>803800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>770100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>478700</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>434900</v>
+      </c>
+      <c r="E18" s="3">
         <v>484900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>562600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>499100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>598900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>442200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>519800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>438400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>347000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>161800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>246600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,113 +1146,120 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E20" s="3">
         <v>12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>586600</v>
+      </c>
+      <c r="E21" s="3">
         <v>607900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>689700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>628900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>717200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>557900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>591500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>469500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>376900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E22" s="3">
         <v>155200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>154200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>117500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>149200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>198300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>61600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,87 +1269,96 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-172900</v>
+      </c>
+      <c r="E23" s="3">
         <v>280500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>392100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>360800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>408400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>194400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>436300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>430700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>337800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>158700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>247900</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E24" s="3">
         <v>118300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>157100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>85500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>99900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>102300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>147400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>92700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>80400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>77300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>51900</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,87 +1395,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-206400</v>
+      </c>
+      <c r="E26" s="3">
         <v>162200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>235000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>275300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>308500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>92100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>288900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>338000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>257400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>81400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>196000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-206400</v>
+      </c>
+      <c r="E27" s="3">
         <v>162200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>235000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>275300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>308500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>92100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>288900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>338000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>257400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>81400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>196000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,87 +1647,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-49800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-206400</v>
+      </c>
+      <c r="E33" s="3">
         <v>162200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>235000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>275300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>308500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>92100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>288900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>338000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>257400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>81400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>196000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,92 +1773,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-206400</v>
+      </c>
+      <c r="E35" s="3">
         <v>162200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>235000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>275300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>308500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>92100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>288900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>338000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>257400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>81400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>196000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,65 +1901,69 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>684200</v>
+      </c>
+      <c r="E41" s="3">
         <v>565800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1029700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>768700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1017000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>520100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>266800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>300500</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>96900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>153400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>140900</v>
+      </c>
+      <c r="E42" s="3">
         <v>19400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>100100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -1884,45 +1973,48 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>167300</v>
+      </c>
+      <c r="E43" s="3">
         <v>187600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>171500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>141100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>143700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>129300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>125700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>161900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,9 +2024,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1962,8 +2057,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1971,108 +2066,117 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E45" s="3">
         <v>69900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>107200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>77900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>61600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>89600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>72000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>67700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1000</v>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1063900</v>
+      </c>
+      <c r="E46" s="3">
         <v>872800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1351100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1024900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1335700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>754500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>477100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>542800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>191700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>224100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E47" s="3">
         <v>30400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>69600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>81900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>25700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2088,77 +2192,83 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>227100</v>
+      </c>
+      <c r="E48" s="3">
         <v>205300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>220200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>229900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>192700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>171900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>140800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
         <v>20300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2121400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2254500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1298400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1165200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1205400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>812500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>830900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>371000</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,33 +2360,36 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E52" s="3">
         <v>157200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>136400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>127400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,9 +2402,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,48 +2444,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3718900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3639200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3175000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2697600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2803300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1776200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1480300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1014800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>373700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>398400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,35 +2525,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E57" s="3">
         <v>58600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>50700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>54100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,38 +2564,41 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E58" s="3">
         <v>37300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>29400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>121000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>148100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>151800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2473,36 +2606,39 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>535600</v>
+      </c>
+      <c r="E59" s="3">
         <v>148100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>127400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>63500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>194100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>189400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>132300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>84000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2512,75 +2648,81 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>967900</v>
+      </c>
+      <c r="E60" s="3">
         <v>558900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>539600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>461800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>569700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>640400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>553900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>435100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>99200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>67700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2494900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2459900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2492200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2505700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2505200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2276800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2372200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2590,27 +2732,30 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>659300</v>
+      </c>
+      <c r="E62" s="3">
         <v>726800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>335100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>252100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,36 +2900,39 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4130300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3770300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3396500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3266200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3181000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3019700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3095800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>550100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,48 +3128,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1251200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-894200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-907600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1142600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1417900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1726400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1818500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>258500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>63100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>196000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,48 +3296,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-411400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-131100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-221500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-568600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-377700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1243500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1615500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>464700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
         <v>269000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>321500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,92 +3380,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-206400</v>
+      </c>
+      <c r="E81" s="3">
         <v>162200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>235000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>275300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>308500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>92100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>288900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>338000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>257400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>81400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>196000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,47 +3490,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E83" s="3">
         <v>46500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,48 +3739,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>567700</v>
+      </c>
+      <c r="E89" s="3">
         <v>490100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>515600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>493700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>551700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>517700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>491900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>452800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>369000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,47 +3802,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-40900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-68300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-54100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-41100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15700</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,48 +3925,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-221700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-782100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-240200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-74600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-609400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-98100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-516500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-141900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-225900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,17 +3988,18 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>150200</v>
+      </c>
+      <c r="E96" s="3">
         <v>111500</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -3777,14 +4010,14 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>2365900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>400000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,124 +4153,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-230000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-167100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-652000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>559700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-181300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-337400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>92000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-15700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>13300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-464000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>261300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-248600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>495400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>251600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-33600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-29000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>236700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
